--- a/Result/profitability/3672.xlsx
+++ b/Result/profitability/3672.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.37125</v>
+        <v>-0.3387499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>33.25</v>
+        <v>34.39875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.91</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1712499999999999</v>
+        <v>-0.205</v>
       </c>
       <c r="N3" t="n">
-        <v>33.58625</v>
+        <v>34.7325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.20125</v>
+        <v>-0.235</v>
       </c>
       <c r="N4" t="n">
-        <v>33.31625</v>
+        <v>34.29375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.23375</v>
+        <v>-0.14375</v>
       </c>
       <c r="N5" t="n">
-        <v>33.13625</v>
+        <v>35.22375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1575</v>
+        <v>-0.18375</v>
       </c>
       <c r="N6" t="n">
-        <v>33.9675</v>
+        <v>33.06625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.20875</v>
+        <v>-0.1575</v>
       </c>
       <c r="N7" t="n">
-        <v>32.035</v>
+        <v>33.5375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8429,6 +8429,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3672</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>49</v>
+      </c>
+      <c r="D64" t="n">
+        <v>29</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-33.17%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-0.505</v>
+      </c>
+      <c r="N64" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-0.03999999999999998</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.1025641025641024</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.2464122137404581</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-0.6260869565217391</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.6923714759535655</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
